--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.02842284282445</v>
+        <v>8.292118711958974</v>
       </c>
       <c r="D2" t="n">
-        <v>51.06318361755496</v>
+        <v>8.297767337852681</v>
       </c>
       <c r="E2" t="n">
-        <v>8.563764972044723</v>
+        <v>1.391611807957267</v>
       </c>
       <c r="F2" t="n">
-        <v>8.564103081122024</v>
+        <v>1.391666750682329</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.1559527869139</v>
+        <v>11.07534232787351</v>
       </c>
       <c r="D3" t="n">
-        <v>68.19138977979901</v>
+        <v>11.08110083921734</v>
       </c>
       <c r="E3" t="n">
-        <v>8.563764972044723</v>
+        <v>1.391611807957267</v>
       </c>
       <c r="F3" t="n">
-        <v>8.564103081122024</v>
+        <v>1.391666750682329</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
